--- a/semiconductor-ml/Data/semiconductor_data_median.xlsx
+++ b/semiconductor-ml/Data/semiconductor_data_median.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4f8f36234d981261/Desktop/Research SemiConductor/Semiconductor-Research-Lab/semiconductor-ml/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="187" documentId="8_{D88DC9AD-478C-4C3A-9E37-765331CAA587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F406F7CE-D045-4341-927A-E0DEFCDC604B}"/>
+  <xr:revisionPtr revIDLastSave="189" documentId="8_{D88DC9AD-478C-4C3A-9E37-765331CAA587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22C5D185-B2F8-4ECD-8DB9-49F83B36B2BA}"/>
   <bookViews>
-    <workbookView xWindow="51720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E44869B-80BF-41E9-806D-DCA141B48975}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="20928" windowHeight="12432" xr2:uid="{7E44869B-80BF-41E9-806D-DCA141B48975}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -161,6 +161,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
